--- a/workbooks/hypothesis-test-workbench.xlsx
+++ b/workbooks/hypothesis-test-workbench.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="84" customWidth="1" min="1" max="1"/>
@@ -488,161 +488,185 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Excel has no function that runs a hypothesis test from summary statistics.</t>
+          <t>FIRST: if there is a yellow 'PROTECTED VIEW' bar at the top of this window,</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T.TEST needs two ranges of raw data, and so does the Analysis ToolPak. When a</t>
+          <t>click Enable Editing. Excel opens downloaded files read-only, and the</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question gives you only n, the mean and the standard deviation, you have to</t>
+          <t>input cells will not accept anything until you do.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>build the test out of cell formulas. That is what these sheets do.</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Excel has no function that runs a hypothesis test from summary statistics.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>How to use a sheet</t>
+          <t>T.TEST needs two ranges of raw data, and so does the Analysis ToolPak. When a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Pick the sheet matching your test (see the chooser below).</t>
+          <t>question gives you only n, the mean and the standard deviation, you have to</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Type your numbers into the yellow cells only.</t>
+          <t>build the test out of cell formulas. That is what these sheets do.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. Read the test statistic, the critical value and the p-value.</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Check that both verdicts agree. They always should.</t>
+          <t>How to use a sheet</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Pick the sheet matching your test (see the chooser below).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Which test do I need?</t>
+          <t xml:space="preserve">  2. Type your numbers into the yellow cells only.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Comparing one sample mean to a known population mean</t>
+          <t xml:space="preserve">  3. Read the test statistic, the critical value and the p-value.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">      population sd known ................ One-Sample Z</t>
+          <t xml:space="preserve">  4. Check that both verdicts agree. They always should.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      population sd unknown .............. One-Sample T</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Comparing two independent groups</t>
+          <t>Which test do I need?</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">      population sds known, or n large ... Two-Sample Z</t>
+          <t xml:space="preserve">  Comparing one sample mean to a known population mean</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      population sds unknown ............. Two-Sample T</t>
+          <t xml:space="preserve">      population sd known ................ One-Sample Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Same subjects measured twice ........... Paired T</t>
+          <t xml:space="preserve">      population sd unknown .............. One-Sample T</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Two categorical variables .............. Chi-Squared</t>
+          <t xml:space="preserve">  Comparing two independent groups</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Is a regression coefficient real? ...... Regression Coefficient T</t>
+          <t xml:space="preserve">      population sds known, or n large ... Two-Sample Z</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      population sds unknown ............. Two-Sample T</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Every sheet reports both the critical-value route and the p-value route.</t>
+          <t xml:space="preserve">  Same subjects measured twice ........... Paired T</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>They are two ways of asking the same question, and a result you can reach</t>
+          <t xml:space="preserve">  Two categorical variables .............. Chi-Squared</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Is a regression coefficient real? ...... Regression Coefficient T</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Every sheet reports both the critical-value route and the p-value route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>They are two ways of asking the same question, and a result you can reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>two ways is more trustworthy than one you can only reach one way.</t>
         </is>

--- a/workbooks/hypothesis-test-workbench.xlsx
+++ b/workbooks/hypothesis-test-workbench.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="84" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Excel has no function that runs a hypothesis test from summary statistics.</t>
+          <t>No Excel function runs a hypothesis test from summary statistics.</t>
         </is>
       </c>
     </row>
@@ -526,14 +526,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question gives you only n, the mean and the standard deviation, you have to</t>
+          <t>question gives you only n, the mean and the standard deviation, you must</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>build the test out of cell formulas. That is what these sheets do.</t>
+          <t>build the test from separate formulas. These sheets do that for you.</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Check that both verdicts agree. They always should.</t>
+          <t xml:space="preserve">  4. Check that both results agree. They always should.</t>
         </is>
       </c>
     </row>
@@ -654,21 +654,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Every sheet reports both the critical-value route and the p-value route.</t>
+          <t>Every sheet gives both the critical value and the p-value. They always</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>They are two ways of asking the same question, and a result you can reach</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>two ways is more trustworthy than one you can only reach one way.</t>
+          <t>agree, so you can use one to check the other.</t>
         </is>
       </c>
     </row>
@@ -850,7 +843,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>two-tailed splits alpha between the tails</t>
+          <t>a two-tailed test divides alpha between the tails</t>
         </is>
       </c>
     </row>
@@ -866,7 +859,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>probability of a result at least this extreme if H0 is true</t>
+          <t>the probability of a result this extreme if H0 is true</t>
         </is>
       </c>
     </row>
@@ -905,7 +898,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Reject when p &lt; alpha.</t>
+          <t>Reject H0 if p is less than alpha.</t>
         </is>
       </c>
     </row>
@@ -921,14 +914,14 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>These two always agree. If they don't, an input is wrong.</t>
+          <t>These two always agree. If they do not, check your inputs.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Remember: failing to reject H0 is not the same as proving it true.</t>
+          <t>Note: failing to reject H0 does not prove that H0 is true.</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1104,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>T.INV.2T already halves alpha - do not halve it yourself</t>
+          <t>T.INV.2T divides alpha for you - do not divide it yourself</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1154,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Reject when p &lt; alpha.</t>
+          <t>Reject H0 if p is less than alpha.</t>
         </is>
       </c>
     </row>
@@ -1177,14 +1170,14 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>These two always agree. If they don't, an input is wrong.</t>
+          <t>These two always agree. If they do not, check your inputs.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Remember: failing to reject H0 is not the same as proving it true.</t>
+          <t>Note: failing to reject H0 does not prove that H0 is true.</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1404,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Reject when p &lt; alpha.</t>
+          <t>Reject H0 if p is less than alpha.</t>
         </is>
       </c>
     </row>
@@ -1427,21 +1420,21 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>These two always agree. If they don't, an input is wrong.</t>
+          <t>These two always agree. If they do not, check your inputs.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Remember: failing to reject H0 is not the same as proving it true.</t>
+          <t>Note: failing to reject H0 does not prove that H0 is true.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Note: with unknown population sds a t-test is the more standard choice. At these sample sizes the two give nearly the same answer.</t>
+          <t>Note: when the population sds are unknown, a t-test is the usual choice. At these sample sizes both give nearly the same answer.</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1584,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>when both sds are equal this is just that value</t>
+          <t>if both sds are equal, this equals that value</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1683,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Reject when p &lt; alpha.</t>
+          <t>Reject H0 if p is less than alpha.</t>
         </is>
       </c>
     </row>
@@ -1706,14 +1699,14 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>These two always agree. If they don't, an input is wrong.</t>
+          <t>These two always agree. If they do not, check your inputs.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Remember: failing to reject H0 is not the same as proving it true.</t>
+          <t>Note: failing to reject H0 does not prove that H0 is true.</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1938,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Reject when p &lt; alpha.</t>
+          <t>Reject H0 if p is less than alpha.</t>
         </is>
       </c>
     </row>
@@ -1961,21 +1954,21 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>These two always agree. If they don't, an input is wrong.</t>
+          <t>These two always agree. If they do not, check your inputs.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Remember: failing to reject H0 is not the same as proving it true.</t>
+          <t>Note: failing to reject H0 does not prove that H0 is true.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>If you have both raw columns you can cross-check with =T.TEST(range1, range2, 2, 1) - the 1 means paired.</t>
+          <t>If you have both raw columns, check the result with =T.TEST(range1, range2, 2, 1). The 1 means paired.</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2116,7 +2109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CHISQ.INV.RT, not CHI.INV.RT - the latter does not exist</t>
+          <t>use CHISQ.INV.RT - there is no function called CHI.INV.RT</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2159,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Reject when p &lt; alpha.</t>
+          <t>Reject H0 if p is less than alpha.</t>
         </is>
       </c>
     </row>
@@ -2182,35 +2175,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>These two always agree. If they don't, an input is wrong.</t>
+          <t>These two always agree. If they do not, check your inputs.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Remember: failing to reject H0 is not the same as proving it true.</t>
+          <t>Note: failing to reject H0 does not prove that H0 is true.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Chi-squared is never two-tailed: the statistic cannot be negative, so there is no left tail.</t>
+          <t>A chi-squared test is never two-tailed. The statistic cannot be negative,</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>If any expected value is below 5, pool similar categories together and recount the</t>
+          <t>so there is no left tail.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>degrees of freedom before using this sheet.</t>
+          <t>If any expected value is below 5, combine similar categories first, then</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>recount the degrees of freedom.</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Reject when p &lt; alpha.</t>
+          <t>Reject H0 if p is less than alpha.</t>
         </is>
       </c>
     </row>
@@ -2470,14 +2470,14 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>These two always agree. If they don't, an input is wrong.</t>
+          <t>These two always agree. If they do not, check your inputs.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Remember: failing to reject H0 is not the same as proving it true.</t>
+          <t>Note: failing to reject H0 does not prove that H0 is true.</t>
         </is>
       </c>
     </row>
